--- a/artfynd/A 35247-2026 artfynd.xlsx
+++ b/artfynd/A 35247-2026 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -761,12 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mänga dagliga obsar under 4 av 10 dagar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -829,11 +830,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -875,12 +872,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera obs under 5 av 10 dagar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,11 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -989,17 +987,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera lockläten under 8 av 10 dagar</t>
+          <t>Flera lockläten under 5 av 10 dagar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 35247-2026 artfynd.xlsx
+++ b/artfynd/A 35247-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243026</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137243040</v>
       </c>
       <c r="B3" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>137243036</v>
       </c>
       <c r="B4" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35247-2026 artfynd.xlsx
+++ b/artfynd/A 35247-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243026</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137243040</v>
       </c>
       <c r="B3" t="n">
-        <v>58577</v>
+        <v>58579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>137243036</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35247-2026 artfynd.xlsx
+++ b/artfynd/A 35247-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243026</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137243040</v>
       </c>
       <c r="B3" t="n">
-        <v>58579</v>
+        <v>58581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>137243036</v>
       </c>
       <c r="B4" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35247-2026 artfynd.xlsx
+++ b/artfynd/A 35247-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137243026</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137243040</v>
       </c>
       <c r="B3" t="n">
-        <v>58581</v>
+        <v>58584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>137243036</v>
       </c>
       <c r="B4" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
